--- a/РАБОЧИЙ СТОЛ/расчет Останкино КИ/матрица Ост КИ/матрица Ост КИ.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчет Останкино КИ/матрица Ост КИ/матрица Ост КИ.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет Останкино КИ\матрица Ост КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчет Останкино КИ\матрица Ост КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C05CAAF2-618B-4031-BD3A-FBB6980190FA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AAAC7CD-F906-4ECE-93FF-4800D20328AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,16 +18,10 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$2:$O$117</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -675,9 +669,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -967,6 +961,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:O120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3342,7 +3337,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="13" t="s">
         <v>33</v>
       </c>
@@ -4194,7 +4189,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
         <v>32</v>
       </c>
@@ -4322,7 +4317,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>123</v>
       </c>
@@ -4356,7 +4351,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>128</v>
       </c>
@@ -4394,7 +4389,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>41</v>
       </c>
@@ -4480,7 +4475,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>143</v>
       </c>
@@ -4516,7 +4511,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>35</v>
       </c>
@@ -4556,7 +4551,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>125</v>
       </c>
@@ -4592,7 +4587,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>19</v>
       </c>
@@ -4634,7 +4629,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="13" t="s">
         <v>73</v>
       </c>
@@ -4670,7 +4665,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="13" t="s">
         <v>34</v>
       </c>
@@ -4718,7 +4713,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>126</v>
       </c>
@@ -4754,7 +4749,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>88</v>
       </c>
@@ -4792,7 +4787,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="13" t="s">
         <v>86</v>
       </c>
@@ -4838,7 +4833,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>56</v>
       </c>
@@ -4918,7 +4913,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>50</v>
       </c>
@@ -5028,7 +5023,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="13" t="s">
         <v>8</v>
       </c>
@@ -5062,7 +5057,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="13" t="s">
         <v>13</v>
       </c>
@@ -5098,7 +5093,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="13" t="s">
         <v>23</v>
       </c>
@@ -5134,7 +5129,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="13" t="s">
         <v>26</v>
       </c>
@@ -5172,7 +5167,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="13" t="s">
         <v>29</v>
       </c>
@@ -5220,7 +5215,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="13" t="s">
         <v>30</v>
       </c>
@@ -5254,7 +5249,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>48</v>
       </c>
@@ -5288,7 +5283,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="13" t="s">
         <v>52</v>
       </c>
@@ -5322,7 +5317,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>60</v>
       </c>
@@ -5356,7 +5351,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>69</v>
       </c>
@@ -5392,7 +5387,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>127</v>
       </c>
@@ -5474,7 +5469,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="13" t="s">
         <v>92</v>
       </c>
@@ -5660,6 +5655,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:O117" xr:uid="{6E3B6DB2-5DDE-4D9F-BCFF-788575683F9A}">
+    <filterColumn colId="14">
+      <filters>
+        <filter val="матрица"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O116">
       <sortCondition descending="1" ref="N2"/>
     </sortState>
